--- a/北京中心顾问薪酬绩效台账_v3.xlsx
+++ b/北京中心顾问薪酬绩效台账_v3.xlsx
@@ -26341,7 +26341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS143"/>
+  <dimension ref="A1:AS141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="16.3984375" customWidth="1" min="1" max="1"/>
@@ -33488,7 +33488,7 @@
       </c>
       <c r="B62" s="53" t="inlineStr">
         <is>
-          <t>姚斯元</t>
+          <t>徐振东</t>
         </is>
       </c>
       <c r="C62" s="53" t="inlineStr">
@@ -33527,57 +33527,45 @@
         <v/>
       </c>
       <c r="K62" s="54" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="L62" s="54" t="n">
-        <v>21604</v>
+        <v>30480.5</v>
       </c>
       <c r="M62" s="54" t="n">
-        <v>0</v>
+        <v>5680</v>
       </c>
       <c r="N62" s="54" t="n">
-        <v>21604</v>
-      </c>
-      <c r="O62" s="55" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="P62" s="54" t="n">
-        <v>16624</v>
-      </c>
+        <v>24800.5</v>
+      </c>
+      <c r="O62" s="55" t="n">
+        <v>0.248005</v>
+      </c>
+      <c r="P62" s="54" t="n"/>
       <c r="Q62" s="55" t="n"/>
-      <c r="R62" s="54" t="n"/>
+      <c r="R62" s="54" t="n">
+        <v>3000</v>
+      </c>
       <c r="S62" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="T62" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="55" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V62" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="T62" s="54" t="n"/>
+      <c r="U62" s="55" t="n"/>
+      <c r="V62" s="54" t="n"/>
       <c r="W62" s="54" t="n">
         <v>0</v>
       </c>
       <c r="X62" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="Y62" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="54" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="Y62" s="54" t="n"/>
+      <c r="Z62" s="54" t="n"/>
       <c r="AA62" s="54" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="AB62" s="54" t="n"/>
       <c r="AC62" s="54" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="AD62" s="54">
         <f>Y62*Z62+AA62*AB62</f>
@@ -33589,7 +33577,7 @@
         <v>2000</v>
       </c>
       <c r="AH62" s="54" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AI62" s="51" t="n"/>
       <c r="AJ62" s="51" t="n"/>
@@ -33605,11 +33593,11 @@
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="52" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B63" s="53" t="inlineStr">
         <is>
-          <t>徐振东</t>
+          <t>刘晓娟</t>
         </is>
       </c>
       <c r="C63" s="53" t="inlineStr">
@@ -33648,52 +33636,70 @@
         <v/>
       </c>
       <c r="K63" s="54" t="n">
-        <v>100000</v>
+        <v>232142</v>
       </c>
       <c r="L63" s="54" t="n">
-        <v>30480.5</v>
+        <v>420139.6</v>
       </c>
       <c r="M63" s="54" t="n">
-        <v>5680</v>
+        <v>50569.1</v>
       </c>
       <c r="N63" s="54" t="n">
-        <v>24800.5</v>
+        <v>369570.5</v>
       </c>
       <c r="O63" s="55" t="n">
-        <v>0.248005</v>
-      </c>
-      <c r="P63" s="54" t="n"/>
-      <c r="Q63" s="55" t="n"/>
+        <v>1.59200187816078</v>
+      </c>
+      <c r="P63" s="54" t="n">
+        <v>357910.5</v>
+      </c>
+      <c r="Q63" s="55" t="n">
+        <v>0.05</v>
+      </c>
       <c r="R63" s="54" t="n">
-        <v>3000</v>
+        <v>17895.525</v>
       </c>
       <c r="S63" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="54" t="n"/>
-      <c r="U63" s="55" t="n"/>
-      <c r="V63" s="54" t="n"/>
+        <v>1.49</v>
+      </c>
+      <c r="T63" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V63" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="W63" s="54" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="X63" s="54" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="Y63" s="54" t="n"/>
-      <c r="Z63" s="54" t="n"/>
+      <c r="Z63" s="54" t="n">
+        <v>0.03</v>
+      </c>
       <c r="AA63" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" s="54" t="n"/>
+        <v>11660</v>
+      </c>
+      <c r="AB63" s="54" t="n">
+        <v>0.048</v>
+      </c>
       <c r="AC63" s="54" t="n">
-        <v>0</v>
+        <v>11660</v>
       </c>
       <c r="AD63" s="54">
         <f>Y63*Z63+AA63*AB63</f>
         <v/>
       </c>
-      <c r="AE63" s="54" t="n"/>
-      <c r="AF63" s="54" t="n"/>
+      <c r="AE63" s="54" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF63" s="54" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AG63" s="54" t="n">
         <v>2000</v>
       </c>
@@ -33714,11 +33720,11 @@
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="52" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B64" s="53" t="inlineStr">
         <is>
-          <t>徐晗</t>
+          <t>房国超</t>
         </is>
       </c>
       <c r="C64" s="53" t="inlineStr">
@@ -33757,33 +33763,35 @@
         <v/>
       </c>
       <c r="K64" s="54" t="n">
-        <v>0</v>
+        <v>232142</v>
       </c>
       <c r="L64" s="54" t="n">
-        <v>47164</v>
+        <v>551499</v>
       </c>
       <c r="M64" s="54" t="n">
-        <v>0</v>
+        <v>59029.1</v>
       </c>
       <c r="N64" s="54" t="n">
-        <v>47164</v>
-      </c>
-      <c r="O64" s="55" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="P64" s="54" t="n"/>
+        <v>492469.9</v>
+      </c>
+      <c r="O64" s="55" t="n">
+        <v>2.12141663292295</v>
+      </c>
+      <c r="P64" s="54" t="n">
+        <v>467969.9</v>
+      </c>
       <c r="Q64" s="55" t="n">
         <v>0.05</v>
       </c>
       <c r="R64" s="54" t="n">
-        <v>0</v>
+        <v>23398.495</v>
       </c>
       <c r="S64" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="54" t="n"/>
+        <v>13.64</v>
+      </c>
+      <c r="T64" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="U64" s="55" t="n">
         <v>0.03</v>
       </c>
@@ -33794,30 +33802,38 @@
         <v>0</v>
       </c>
       <c r="X64" s="54" t="n">
-        <v>6000</v>
-      </c>
-      <c r="Y64" s="54" t="n"/>
+        <v>28000</v>
+      </c>
+      <c r="Y64" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="Z64" s="54" t="n">
         <v>0.03</v>
       </c>
       <c r="AA64" s="54" t="n">
-        <v>5680</v>
-      </c>
-      <c r="AB64" s="54" t="n"/>
+        <v>24500</v>
+      </c>
+      <c r="AB64" s="54" t="n">
+        <v>0.05</v>
+      </c>
       <c r="AC64" s="54" t="n">
-        <v>5680</v>
+        <v>24500</v>
       </c>
       <c r="AD64" s="54">
         <f>Y64*Z64+AA64*AB64</f>
         <v/>
       </c>
-      <c r="AE64" s="54" t="n"/>
-      <c r="AF64" s="54" t="n"/>
+      <c r="AE64" s="54" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF64" s="54" t="n">
+        <v>0.85</v>
+      </c>
       <c r="AG64" s="54" t="n">
         <v>2000</v>
       </c>
       <c r="AH64" s="54" t="n">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="AI64" s="51" t="n"/>
       <c r="AJ64" s="51" t="n"/>
@@ -33837,7 +33853,7 @@
       </c>
       <c r="B65" s="53" t="inlineStr">
         <is>
-          <t>刘晓娟</t>
+          <t>王磊</t>
         </is>
       </c>
       <c r="C65" s="53" t="inlineStr">
@@ -33876,31 +33892,31 @@
         <v/>
       </c>
       <c r="K65" s="54" t="n">
-        <v>232142</v>
+        <v>185714</v>
       </c>
       <c r="L65" s="54" t="n">
-        <v>420139.6</v>
+        <v>216909.2</v>
       </c>
       <c r="M65" s="54" t="n">
-        <v>50569.1</v>
+        <v>20691.2</v>
       </c>
       <c r="N65" s="54" t="n">
-        <v>369570.5</v>
+        <v>196218</v>
       </c>
       <c r="O65" s="55" t="n">
-        <v>1.59200187816078</v>
+        <v>1.05656008701552</v>
       </c>
       <c r="P65" s="54" t="n">
-        <v>357910.5</v>
+        <v>196218</v>
       </c>
       <c r="Q65" s="55" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="R65" s="54" t="n">
-        <v>17895.525</v>
+        <v>5886.54</v>
       </c>
       <c r="S65" s="54" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T65" s="54" t="n">
         <v>0</v>
@@ -33912,34 +33928,32 @@
         <v>0</v>
       </c>
       <c r="W65" s="54" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="X65" s="54" t="n">
-        <v>28000</v>
-      </c>
-      <c r="Y65" s="54" t="n"/>
+        <v>15000</v>
+      </c>
+      <c r="Y65" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="Z65" s="54" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="AA65" s="54" t="n">
-        <v>11660</v>
+        <v>0</v>
       </c>
       <c r="AB65" s="54" t="n">
-        <v>0.048</v>
+        <v>0.028</v>
       </c>
       <c r="AC65" s="54" t="n">
-        <v>11660</v>
+        <v>0</v>
       </c>
       <c r="AD65" s="54">
         <f>Y65*Z65+AA65*AB65</f>
         <v/>
       </c>
-      <c r="AE65" s="54" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF65" s="54" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="AE65" s="54" t="n"/>
+      <c r="AF65" s="54" t="n"/>
       <c r="AG65" s="54" t="n">
         <v>2000</v>
       </c>
@@ -33964,7 +33978,7 @@
       </c>
       <c r="B66" s="53" t="inlineStr">
         <is>
-          <t>房国超</t>
+          <t>田一禾</t>
         </is>
       </c>
       <c r="C66" s="53" t="inlineStr">
@@ -34006,28 +34020,28 @@
         <v>232142</v>
       </c>
       <c r="L66" s="54" t="n">
-        <v>551499</v>
+        <v>427600.6</v>
       </c>
       <c r="M66" s="54" t="n">
-        <v>59029.1</v>
+        <v>9017</v>
       </c>
       <c r="N66" s="54" t="n">
-        <v>492469.9</v>
+        <v>418583.6</v>
       </c>
       <c r="O66" s="55" t="n">
-        <v>2.12141663292295</v>
+        <v>1.80313601157912</v>
       </c>
       <c r="P66" s="54" t="n">
-        <v>467969.9</v>
+        <v>418583.6</v>
       </c>
       <c r="Q66" s="55" t="n">
         <v>0.05</v>
       </c>
       <c r="R66" s="54" t="n">
-        <v>23398.495</v>
+        <v>20929.18</v>
       </c>
       <c r="S66" s="54" t="n">
-        <v>13.64</v>
+        <v>0</v>
       </c>
       <c r="T66" s="54" t="n">
         <v>0</v>
@@ -34051,29 +34065,29 @@
         <v>0.03</v>
       </c>
       <c r="AA66" s="54" t="n">
-        <v>24500</v>
+        <v>0</v>
       </c>
       <c r="AB66" s="54" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="AC66" s="54" t="n">
-        <v>24500</v>
+        <v>0</v>
       </c>
       <c r="AD66" s="54">
         <f>Y66*Z66+AA66*AB66</f>
         <v/>
       </c>
       <c r="AE66" s="54" t="n">
-        <v>85</v>
+        <v>62.2</v>
       </c>
       <c r="AF66" s="54" t="n">
-        <v>0.85</v>
+        <v>0.622</v>
       </c>
       <c r="AG66" s="54" t="n">
         <v>2000</v>
       </c>
       <c r="AH66" s="54" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="AI66" s="51" t="n"/>
       <c r="AJ66" s="51" t="n"/>
@@ -34093,7 +34107,7 @@
       </c>
       <c r="B67" s="53" t="inlineStr">
         <is>
-          <t>王磊</t>
+          <t>黄智超</t>
         </is>
       </c>
       <c r="C67" s="53" t="inlineStr">
@@ -34132,31 +34146,31 @@
         <v/>
       </c>
       <c r="K67" s="54" t="n">
-        <v>185714</v>
+        <v>232142</v>
       </c>
       <c r="L67" s="54" t="n">
-        <v>216909.2</v>
+        <v>280758.1</v>
       </c>
       <c r="M67" s="54" t="n">
-        <v>20691.2</v>
+        <v>15620</v>
       </c>
       <c r="N67" s="54" t="n">
-        <v>196218</v>
+        <v>265138.1</v>
       </c>
       <c r="O67" s="55" t="n">
-        <v>1.05656008701552</v>
+        <v>1.14213757096949</v>
       </c>
       <c r="P67" s="54" t="n">
-        <v>196218</v>
+        <v>261658.1</v>
       </c>
       <c r="Q67" s="55" t="n">
         <v>0.03</v>
       </c>
       <c r="R67" s="54" t="n">
-        <v>5886.54</v>
+        <v>7849.743</v>
       </c>
       <c r="S67" s="54" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="T67" s="54" t="n">
         <v>0</v>
@@ -34171,7 +34185,7 @@
         <v>0</v>
       </c>
       <c r="X67" s="54" t="n">
-        <v>15000</v>
+        <v>28000</v>
       </c>
       <c r="Y67" s="54" t="n">
         <v>0</v>
@@ -34180,25 +34194,29 @@
         <v>0.028</v>
       </c>
       <c r="AA67" s="54" t="n">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="AB67" s="54" t="n">
-        <v>0.028</v>
+        <v>0.04</v>
       </c>
       <c r="AC67" s="54" t="n">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="AD67" s="54">
         <f>Y67*Z67+AA67*AB67</f>
         <v/>
       </c>
-      <c r="AE67" s="54" t="n"/>
-      <c r="AF67" s="54" t="n"/>
+      <c r="AE67" s="54" t="n">
+        <v>83.0285714285714</v>
+      </c>
+      <c r="AF67" s="54" t="n">
+        <v>0.830285714285714</v>
+      </c>
       <c r="AG67" s="54" t="n">
         <v>2000</v>
       </c>
       <c r="AH67" s="54" t="n">
-        <v>2000</v>
+        <v>1660.57142857143</v>
       </c>
       <c r="AI67" s="51" t="n"/>
       <c r="AJ67" s="51" t="n"/>
@@ -34218,7 +34236,7 @@
       </c>
       <c r="B68" s="53" t="inlineStr">
         <is>
-          <t>田一禾</t>
+          <t>徐振东</t>
         </is>
       </c>
       <c r="C68" s="53" t="inlineStr">
@@ -34257,59 +34275,43 @@
         <v/>
       </c>
       <c r="K68" s="54" t="n">
-        <v>232142</v>
+        <v>116076</v>
       </c>
       <c r="L68" s="54" t="n">
-        <v>427600.6</v>
+        <v>40820</v>
       </c>
       <c r="M68" s="54" t="n">
-        <v>9017</v>
+        <v>3924.4</v>
       </c>
       <c r="N68" s="54" t="n">
-        <v>418583.6</v>
+        <v>36895.6</v>
       </c>
       <c r="O68" s="55" t="n">
-        <v>1.80313601157912</v>
+        <v>0.317857265929219</v>
       </c>
       <c r="P68" s="54" t="n">
-        <v>418583.6</v>
-      </c>
-      <c r="Q68" s="55" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="R68" s="54" t="n">
-        <v>20929.18</v>
-      </c>
+        <v>36895.6</v>
+      </c>
+      <c r="Q68" s="55" t="n"/>
+      <c r="R68" s="54" t="n"/>
       <c r="S68" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="T68" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="55" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V68" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="T68" s="54" t="n"/>
+      <c r="U68" s="55" t="n"/>
+      <c r="V68" s="54" t="n"/>
       <c r="W68" s="54" t="n">
         <v>0</v>
       </c>
       <c r="X68" s="54" t="n">
-        <v>28000</v>
-      </c>
-      <c r="Y68" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" s="54" t="n">
-        <v>0.03</v>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="Y68" s="54" t="n"/>
+      <c r="Z68" s="54" t="n"/>
       <c r="AA68" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="AB68" s="54" t="n">
-        <v>0.048</v>
-      </c>
+      <c r="AB68" s="54" t="n"/>
       <c r="AC68" s="54" t="n">
         <v>0</v>
       </c>
@@ -34317,17 +34319,13 @@
         <f>Y68*Z68+AA68*AB68</f>
         <v/>
       </c>
-      <c r="AE68" s="54" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="AF68" s="54" t="n">
-        <v>0.622</v>
-      </c>
+      <c r="AE68" s="54" t="n"/>
+      <c r="AF68" s="54" t="n"/>
       <c r="AG68" s="54" t="n">
         <v>2000</v>
       </c>
       <c r="AH68" s="54" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AI68" s="51" t="n"/>
       <c r="AJ68" s="51" t="n"/>
@@ -34343,11 +34341,11 @@
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="52" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B69" s="53" t="inlineStr">
         <is>
-          <t>黄智超</t>
+          <t>刘晓娟</t>
         </is>
       </c>
       <c r="C69" s="53" t="inlineStr">
@@ -34386,37 +34384,37 @@
         <v/>
       </c>
       <c r="K69" s="54" t="n">
-        <v>232142</v>
+        <v>400000</v>
       </c>
       <c r="L69" s="54" t="n">
-        <v>280758.1</v>
+        <v>383772.2</v>
       </c>
       <c r="M69" s="54" t="n">
-        <v>15620</v>
+        <v>42614</v>
       </c>
       <c r="N69" s="54" t="n">
-        <v>265138.1</v>
+        <v>341158.2</v>
       </c>
       <c r="O69" s="55" t="n">
-        <v>1.14213757096949</v>
+        <v>0.8528955</v>
       </c>
       <c r="P69" s="54" t="n">
-        <v>261658.1</v>
+        <v>336454.4</v>
       </c>
       <c r="Q69" s="55" t="n">
-        <v>0.03</v>
+        <v>0.018</v>
       </c>
       <c r="R69" s="54" t="n">
-        <v>7849.743</v>
+        <v>6056.1792</v>
       </c>
       <c r="S69" s="54" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="T69" s="54" t="n">
         <v>0</v>
       </c>
       <c r="U69" s="55" t="n">
-        <v>0.03</v>
+        <v>0.018</v>
       </c>
       <c r="V69" s="54" t="n">
         <v>0</v>
@@ -34425,38 +34423,36 @@
         <v>0</v>
       </c>
       <c r="X69" s="54" t="n">
-        <v>28000</v>
-      </c>
-      <c r="Y69" s="54" t="n">
-        <v>0</v>
-      </c>
+        <v>25000</v>
+      </c>
+      <c r="Y69" s="54" t="n"/>
       <c r="Z69" s="54" t="n">
-        <v>0.028</v>
+        <v>0.016</v>
       </c>
       <c r="AA69" s="54" t="n">
-        <v>3480</v>
+        <v>4703.8</v>
       </c>
       <c r="AB69" s="54" t="n">
-        <v>0.04</v>
+        <v>0.016</v>
       </c>
       <c r="AC69" s="54" t="n">
-        <v>3480</v>
+        <v>4703.8</v>
       </c>
       <c r="AD69" s="54">
         <f>Y69*Z69+AA69*AB69</f>
         <v/>
       </c>
       <c r="AE69" s="54" t="n">
-        <v>83.0285714285714</v>
+        <v>90</v>
       </c>
       <c r="AF69" s="54" t="n">
-        <v>0.830285714285714</v>
+        <v>0.9</v>
       </c>
       <c r="AG69" s="54" t="n">
         <v>2000</v>
       </c>
       <c r="AH69" s="54" t="n">
-        <v>1660.57142857143</v>
+        <v>2000</v>
       </c>
       <c r="AI69" s="51" t="n"/>
       <c r="AJ69" s="51" t="n"/>
@@ -34472,11 +34468,11 @@
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="52" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B70" s="53" t="inlineStr">
         <is>
-          <t>徐振东</t>
+          <t>房国超</t>
         </is>
       </c>
       <c r="C70" s="53" t="inlineStr">
@@ -34514,58 +34510,40 @@
         <f>AH70</f>
         <v/>
       </c>
-      <c r="K70" s="54" t="n">
-        <v>116076</v>
-      </c>
-      <c r="L70" s="54" t="n">
-        <v>40820</v>
-      </c>
-      <c r="M70" s="54" t="n">
-        <v>3924.4</v>
-      </c>
-      <c r="N70" s="54" t="n">
-        <v>36895.6</v>
-      </c>
-      <c r="O70" s="55" t="n">
-        <v>0.317857265929219</v>
-      </c>
-      <c r="P70" s="54" t="n">
-        <v>36895.6</v>
-      </c>
+      <c r="K70" s="54" t="n"/>
+      <c r="L70" s="54" t="n"/>
+      <c r="M70" s="54" t="n"/>
+      <c r="N70" s="54" t="n"/>
+      <c r="O70" s="55" t="n"/>
+      <c r="P70" s="54" t="n"/>
       <c r="Q70" s="55" t="n"/>
       <c r="R70" s="54" t="n"/>
-      <c r="S70" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="S70" s="54" t="n"/>
       <c r="T70" s="54" t="n"/>
       <c r="U70" s="55" t="n"/>
       <c r="V70" s="54" t="n"/>
-      <c r="W70" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" s="54" t="n">
-        <v>5000</v>
-      </c>
+      <c r="W70" s="54" t="n"/>
+      <c r="X70" s="54" t="n"/>
       <c r="Y70" s="54" t="n"/>
       <c r="Z70" s="54" t="n"/>
-      <c r="AA70" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA70" s="54" t="n"/>
       <c r="AB70" s="54" t="n"/>
-      <c r="AC70" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC70" s="54" t="n"/>
       <c r="AD70" s="54">
         <f>Y70*Z70+AA70*AB70</f>
         <v/>
       </c>
-      <c r="AE70" s="54" t="n"/>
-      <c r="AF70" s="54" t="n"/>
+      <c r="AE70" s="54" t="n">
+        <v>59</v>
+      </c>
+      <c r="AF70" s="54" t="n">
+        <v>0.59</v>
+      </c>
       <c r="AG70" s="54" t="n">
         <v>2000</v>
       </c>
       <c r="AH70" s="54" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AI70" s="51" t="n"/>
       <c r="AJ70" s="51" t="n"/>
@@ -34585,7 +34563,7 @@
       </c>
       <c r="B71" s="53" t="inlineStr">
         <is>
-          <t>刘晓娟</t>
+          <t>王磊</t>
         </is>
       </c>
       <c r="C71" s="53" t="inlineStr">
@@ -34627,72 +34605,62 @@
         <v>400000</v>
       </c>
       <c r="L71" s="54" t="n">
-        <v>383772.2</v>
+        <v>146020</v>
       </c>
       <c r="M71" s="54" t="n">
-        <v>42614</v>
+        <v>4465</v>
       </c>
       <c r="N71" s="54" t="n">
-        <v>341158.2</v>
+        <v>141555</v>
       </c>
       <c r="O71" s="55" t="n">
-        <v>0.8528955</v>
+        <v>0.3538875</v>
       </c>
       <c r="P71" s="54" t="n">
-        <v>336454.4</v>
-      </c>
-      <c r="Q71" s="55" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="R71" s="54" t="n">
-        <v>6056.1792</v>
-      </c>
+        <v>141555</v>
+      </c>
+      <c r="Q71" s="55" t="n"/>
+      <c r="R71" s="54" t="n"/>
       <c r="S71" s="54" t="n">
         <v>0</v>
       </c>
       <c r="T71" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="U71" s="55" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="V71" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="U71" s="55" t="n"/>
+      <c r="V71" s="54" t="n"/>
       <c r="W71" s="54" t="n">
         <v>0</v>
       </c>
       <c r="X71" s="54" t="n">
         <v>25000</v>
       </c>
-      <c r="Y71" s="54" t="n"/>
-      <c r="Z71" s="54" t="n">
-        <v>0.016</v>
-      </c>
+      <c r="Y71" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="54" t="n"/>
       <c r="AA71" s="54" t="n">
-        <v>4703.8</v>
-      </c>
-      <c r="AB71" s="54" t="n">
-        <v>0.016</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB71" s="54" t="n"/>
       <c r="AC71" s="54" t="n">
-        <v>4703.8</v>
+        <v>0</v>
       </c>
       <c r="AD71" s="54">
         <f>Y71*Z71+AA71*AB71</f>
         <v/>
       </c>
       <c r="AE71" s="54" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="AF71" s="54" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AG71" s="54" t="n">
         <v>2000</v>
       </c>
       <c r="AH71" s="54" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AI71" s="51" t="n"/>
       <c r="AJ71" s="51" t="n"/>
@@ -34712,7 +34680,7 @@
       </c>
       <c r="B72" s="53" t="inlineStr">
         <is>
-          <t>房国超</t>
+          <t>田一禾</t>
         </is>
       </c>
       <c r="C72" s="53" t="inlineStr">
@@ -34750,34 +34718,72 @@
         <f>AH72</f>
         <v/>
       </c>
-      <c r="K72" s="54" t="n"/>
-      <c r="L72" s="54" t="n"/>
-      <c r="M72" s="54" t="n"/>
-      <c r="N72" s="54" t="n"/>
-      <c r="O72" s="55" t="n"/>
-      <c r="P72" s="54" t="n"/>
-      <c r="Q72" s="55" t="n"/>
-      <c r="R72" s="54" t="n"/>
-      <c r="S72" s="54" t="n"/>
-      <c r="T72" s="54" t="n"/>
-      <c r="U72" s="55" t="n"/>
-      <c r="V72" s="54" t="n"/>
-      <c r="W72" s="54" t="n"/>
-      <c r="X72" s="54" t="n"/>
-      <c r="Y72" s="54" t="n"/>
-      <c r="Z72" s="54" t="n"/>
-      <c r="AA72" s="54" t="n"/>
-      <c r="AB72" s="54" t="n"/>
-      <c r="AC72" s="54" t="n"/>
+      <c r="K72" s="54" t="n">
+        <v>400000</v>
+      </c>
+      <c r="L72" s="54" t="n">
+        <v>442620</v>
+      </c>
+      <c r="M72" s="54" t="n">
+        <v>31350.1</v>
+      </c>
+      <c r="N72" s="54" t="n">
+        <v>411269.9</v>
+      </c>
+      <c r="O72" s="55" t="n">
+        <v>1.02817475</v>
+      </c>
+      <c r="P72" s="54" t="n">
+        <v>411269.9</v>
+      </c>
+      <c r="Q72" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R72" s="54" t="n">
+        <v>12338.097</v>
+      </c>
+      <c r="S72" s="54" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T72" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V72" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="54" t="n">
+        <v>25000</v>
+      </c>
+      <c r="Y72" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="54" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="AA72" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="54" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="AC72" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="AD72" s="54">
         <f>Y72*Z72+AA72*AB72</f>
         <v/>
       </c>
       <c r="AE72" s="54" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AF72" s="54" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="AG72" s="54" t="n">
         <v>2000</v>
@@ -34803,7 +34809,7 @@
       </c>
       <c r="B73" s="53" t="inlineStr">
         <is>
-          <t>王磊</t>
+          <t>黄智超</t>
         </is>
       </c>
       <c r="C73" s="53" t="inlineStr">
@@ -34845,30 +34851,38 @@
         <v>400000</v>
       </c>
       <c r="L73" s="54" t="n">
-        <v>146020</v>
+        <v>425912</v>
       </c>
       <c r="M73" s="54" t="n">
-        <v>4465</v>
+        <v>75357.39999999999</v>
       </c>
       <c r="N73" s="54" t="n">
-        <v>141555</v>
+        <v>350554.6</v>
       </c>
       <c r="O73" s="55" t="n">
-        <v>0.3538875</v>
+        <v>0.8763865</v>
       </c>
       <c r="P73" s="54" t="n">
-        <v>141555</v>
-      </c>
-      <c r="Q73" s="55" t="n"/>
-      <c r="R73" s="54" t="n"/>
+        <v>348763.6</v>
+      </c>
+      <c r="Q73" s="55" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="R73" s="54" t="n">
+        <v>6277.7448</v>
+      </c>
       <c r="S73" s="54" t="n">
         <v>0</v>
       </c>
       <c r="T73" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="U73" s="55" t="n"/>
-      <c r="V73" s="54" t="n"/>
+      <c r="U73" s="55" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="V73" s="54" t="n">
+        <v>0</v>
+      </c>
       <c r="W73" s="54" t="n">
         <v>0</v>
       </c>
@@ -34878,29 +34892,33 @@
       <c r="Y73" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="54" t="n"/>
+      <c r="Z73" s="54" t="n">
+        <v>0.016</v>
+      </c>
       <c r="AA73" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" s="54" t="n"/>
+        <v>1791</v>
+      </c>
+      <c r="AB73" s="54" t="n">
+        <v>0.016</v>
+      </c>
       <c r="AC73" s="54" t="n">
-        <v>0</v>
+        <v>1791</v>
       </c>
       <c r="AD73" s="54">
         <f>Y73*Z73+AA73*AB73</f>
         <v/>
       </c>
       <c r="AE73" s="54" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="AF73" s="54" t="n">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AG73" s="54" t="n">
         <v>2000</v>
       </c>
       <c r="AH73" s="54" t="n">
-        <v>0</v>
+        <v>1520</v>
       </c>
       <c r="AI73" s="51" t="n"/>
       <c r="AJ73" s="51" t="n"/>
@@ -34915,122 +34933,40 @@
       <c r="AS73" s="51" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="52" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B74" s="53" t="inlineStr">
-        <is>
-          <t>田一禾</t>
-        </is>
-      </c>
-      <c r="C74" s="53" t="inlineStr">
-        <is>
-          <t>四六级</t>
-        </is>
-      </c>
-      <c r="D74" s="53" t="inlineStr">
-        <is>
-          <t>四六级项目部</t>
-        </is>
-      </c>
-      <c r="E74" s="53" t="inlineStr">
-        <is>
-          <t>B级学习顾问</t>
-        </is>
-      </c>
-      <c r="F74" s="54">
-        <f>G74+H74+I74+J74</f>
-        <v/>
-      </c>
-      <c r="G74" s="54">
-        <f>R74+S74</f>
-        <v/>
-      </c>
-      <c r="H74" s="54">
-        <f>V74-W74</f>
-        <v/>
-      </c>
-      <c r="I74" s="54">
-        <f>AD74</f>
-        <v/>
-      </c>
-      <c r="J74" s="54">
-        <f>AH74</f>
-        <v/>
-      </c>
-      <c r="K74" s="54" t="n">
-        <v>400000</v>
-      </c>
-      <c r="L74" s="54" t="n">
-        <v>442620</v>
-      </c>
-      <c r="M74" s="54" t="n">
-        <v>31350.1</v>
-      </c>
-      <c r="N74" s="54" t="n">
-        <v>411269.9</v>
-      </c>
-      <c r="O74" s="55" t="n">
-        <v>1.02817475</v>
-      </c>
-      <c r="P74" s="54" t="n">
-        <v>411269.9</v>
-      </c>
-      <c r="Q74" s="55" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R74" s="54" t="n">
-        <v>12338.097</v>
-      </c>
-      <c r="S74" s="54" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T74" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" s="55" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V74" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" s="54" t="n">
-        <v>25000</v>
-      </c>
-      <c r="Y74" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z74" s="54" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="AA74" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB74" s="54" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="AC74" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD74" s="54">
-        <f>Y74*Z74+AA74*AB74</f>
-        <v/>
-      </c>
-      <c r="AE74" s="54" t="n">
-        <v>64</v>
-      </c>
-      <c r="AF74" s="54" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AG74" s="54" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AH74" s="54" t="n">
-        <v>0</v>
-      </c>
+      <c r="A74" s="51" t="n"/>
+      <c r="B74" s="51" t="n"/>
+      <c r="C74" s="51" t="n"/>
+      <c r="D74" s="51" t="n"/>
+      <c r="E74" s="51" t="n"/>
+      <c r="F74" s="51" t="n"/>
+      <c r="G74" s="51" t="n"/>
+      <c r="H74" s="51" t="n"/>
+      <c r="I74" s="51" t="n"/>
+      <c r="J74" s="51" t="n"/>
+      <c r="K74" s="51" t="n"/>
+      <c r="L74" s="51" t="n"/>
+      <c r="M74" s="51" t="n"/>
+      <c r="N74" s="51" t="n"/>
+      <c r="O74" s="51" t="n"/>
+      <c r="P74" s="51" t="n"/>
+      <c r="Q74" s="51" t="n"/>
+      <c r="R74" s="51" t="n"/>
+      <c r="S74" s="51" t="n"/>
+      <c r="T74" s="51" t="n"/>
+      <c r="U74" s="51" t="n"/>
+      <c r="V74" s="51" t="n"/>
+      <c r="W74" s="51" t="n"/>
+      <c r="X74" s="51" t="n"/>
+      <c r="Y74" s="51" t="n"/>
+      <c r="Z74" s="51" t="n"/>
+      <c r="AA74" s="51" t="n"/>
+      <c r="AB74" s="51" t="n"/>
+      <c r="AC74" s="51" t="n"/>
+      <c r="AD74" s="51" t="n"/>
+      <c r="AE74" s="51" t="n"/>
+      <c r="AF74" s="51" t="n"/>
+      <c r="AG74" s="51" t="n"/>
+      <c r="AH74" s="51" t="n"/>
       <c r="AI74" s="51" t="n"/>
       <c r="AJ74" s="51" t="n"/>
       <c r="AK74" s="51" t="n"/>
@@ -35044,122 +34980,40 @@
       <c r="AS74" s="51" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="52" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B75" s="53" t="inlineStr">
-        <is>
-          <t>黄智超</t>
-        </is>
-      </c>
-      <c r="C75" s="53" t="inlineStr">
-        <is>
-          <t>四六级</t>
-        </is>
-      </c>
-      <c r="D75" s="53" t="inlineStr">
-        <is>
-          <t>四六级项目部</t>
-        </is>
-      </c>
-      <c r="E75" s="53" t="inlineStr">
-        <is>
-          <t>B级学习顾问</t>
-        </is>
-      </c>
-      <c r="F75" s="54">
-        <f>G75+H75+I75+J75</f>
-        <v/>
-      </c>
-      <c r="G75" s="54">
-        <f>R75+S75</f>
-        <v/>
-      </c>
-      <c r="H75" s="54">
-        <f>V75-W75</f>
-        <v/>
-      </c>
-      <c r="I75" s="54">
-        <f>AD75</f>
-        <v/>
-      </c>
-      <c r="J75" s="54">
-        <f>AH75</f>
-        <v/>
-      </c>
-      <c r="K75" s="54" t="n">
-        <v>400000</v>
-      </c>
-      <c r="L75" s="54" t="n">
-        <v>425912</v>
-      </c>
-      <c r="M75" s="54" t="n">
-        <v>75357.39999999999</v>
-      </c>
-      <c r="N75" s="54" t="n">
-        <v>350554.6</v>
-      </c>
-      <c r="O75" s="55" t="n">
-        <v>0.8763865</v>
-      </c>
-      <c r="P75" s="54" t="n">
-        <v>348763.6</v>
-      </c>
-      <c r="Q75" s="55" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="R75" s="54" t="n">
-        <v>6277.7448</v>
-      </c>
-      <c r="S75" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" s="55" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="V75" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" s="54" t="n">
-        <v>25000</v>
-      </c>
-      <c r="Y75" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z75" s="54" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="AA75" s="54" t="n">
-        <v>1791</v>
-      </c>
-      <c r="AB75" s="54" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="AC75" s="54" t="n">
-        <v>1791</v>
-      </c>
-      <c r="AD75" s="54">
-        <f>Y75*Z75+AA75*AB75</f>
-        <v/>
-      </c>
-      <c r="AE75" s="54" t="n">
-        <v>76</v>
-      </c>
-      <c r="AF75" s="54" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="AG75" s="54" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AH75" s="54" t="n">
-        <v>1520</v>
-      </c>
+      <c r="A75" s="51" t="n"/>
+      <c r="B75" s="51" t="n"/>
+      <c r="C75" s="51" t="n"/>
+      <c r="D75" s="51" t="n"/>
+      <c r="E75" s="51" t="n"/>
+      <c r="F75" s="51" t="n"/>
+      <c r="G75" s="51" t="n"/>
+      <c r="H75" s="51" t="n"/>
+      <c r="I75" s="51" t="n"/>
+      <c r="J75" s="51" t="n"/>
+      <c r="K75" s="51" t="n"/>
+      <c r="L75" s="51" t="n"/>
+      <c r="M75" s="51" t="n"/>
+      <c r="N75" s="51" t="n"/>
+      <c r="O75" s="51" t="n"/>
+      <c r="P75" s="51" t="n"/>
+      <c r="Q75" s="51" t="n"/>
+      <c r="R75" s="51" t="n"/>
+      <c r="S75" s="51" t="n"/>
+      <c r="T75" s="51" t="n"/>
+      <c r="U75" s="51" t="n"/>
+      <c r="V75" s="51" t="n"/>
+      <c r="W75" s="51" t="n"/>
+      <c r="X75" s="51" t="n"/>
+      <c r="Y75" s="51" t="n"/>
+      <c r="Z75" s="51" t="n"/>
+      <c r="AA75" s="51" t="n"/>
+      <c r="AB75" s="51" t="n"/>
+      <c r="AC75" s="51" t="n"/>
+      <c r="AD75" s="51" t="n"/>
+      <c r="AE75" s="51" t="n"/>
+      <c r="AF75" s="51" t="n"/>
+      <c r="AG75" s="51" t="n"/>
+      <c r="AH75" s="51" t="n"/>
       <c r="AI75" s="51" t="n"/>
       <c r="AJ75" s="51" t="n"/>
       <c r="AK75" s="51" t="n"/>
@@ -38273,100 +38127,6 @@
       <c r="AQ141" s="51" t="n"/>
       <c r="AR141" s="51" t="n"/>
       <c r="AS141" s="51" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="51" t="n"/>
-      <c r="B142" s="51" t="n"/>
-      <c r="C142" s="51" t="n"/>
-      <c r="D142" s="51" t="n"/>
-      <c r="E142" s="51" t="n"/>
-      <c r="F142" s="51" t="n"/>
-      <c r="G142" s="51" t="n"/>
-      <c r="H142" s="51" t="n"/>
-      <c r="I142" s="51" t="n"/>
-      <c r="J142" s="51" t="n"/>
-      <c r="K142" s="51" t="n"/>
-      <c r="L142" s="51" t="n"/>
-      <c r="M142" s="51" t="n"/>
-      <c r="N142" s="51" t="n"/>
-      <c r="O142" s="51" t="n"/>
-      <c r="P142" s="51" t="n"/>
-      <c r="Q142" s="51" t="n"/>
-      <c r="R142" s="51" t="n"/>
-      <c r="S142" s="51" t="n"/>
-      <c r="T142" s="51" t="n"/>
-      <c r="U142" s="51" t="n"/>
-      <c r="V142" s="51" t="n"/>
-      <c r="W142" s="51" t="n"/>
-      <c r="X142" s="51" t="n"/>
-      <c r="Y142" s="51" t="n"/>
-      <c r="Z142" s="51" t="n"/>
-      <c r="AA142" s="51" t="n"/>
-      <c r="AB142" s="51" t="n"/>
-      <c r="AC142" s="51" t="n"/>
-      <c r="AD142" s="51" t="n"/>
-      <c r="AE142" s="51" t="n"/>
-      <c r="AF142" s="51" t="n"/>
-      <c r="AG142" s="51" t="n"/>
-      <c r="AH142" s="51" t="n"/>
-      <c r="AI142" s="51" t="n"/>
-      <c r="AJ142" s="51" t="n"/>
-      <c r="AK142" s="51" t="n"/>
-      <c r="AL142" s="51" t="n"/>
-      <c r="AM142" s="51" t="n"/>
-      <c r="AN142" s="51" t="n"/>
-      <c r="AO142" s="51" t="n"/>
-      <c r="AP142" s="51" t="n"/>
-      <c r="AQ142" s="51" t="n"/>
-      <c r="AR142" s="51" t="n"/>
-      <c r="AS142" s="51" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="51" t="n"/>
-      <c r="B143" s="51" t="n"/>
-      <c r="C143" s="51" t="n"/>
-      <c r="D143" s="51" t="n"/>
-      <c r="E143" s="51" t="n"/>
-      <c r="F143" s="51" t="n"/>
-      <c r="G143" s="51" t="n"/>
-      <c r="H143" s="51" t="n"/>
-      <c r="I143" s="51" t="n"/>
-      <c r="J143" s="51" t="n"/>
-      <c r="K143" s="51" t="n"/>
-      <c r="L143" s="51" t="n"/>
-      <c r="M143" s="51" t="n"/>
-      <c r="N143" s="51" t="n"/>
-      <c r="O143" s="51" t="n"/>
-      <c r="P143" s="51" t="n"/>
-      <c r="Q143" s="51" t="n"/>
-      <c r="R143" s="51" t="n"/>
-      <c r="S143" s="51" t="n"/>
-      <c r="T143" s="51" t="n"/>
-      <c r="U143" s="51" t="n"/>
-      <c r="V143" s="51" t="n"/>
-      <c r="W143" s="51" t="n"/>
-      <c r="X143" s="51" t="n"/>
-      <c r="Y143" s="51" t="n"/>
-      <c r="Z143" s="51" t="n"/>
-      <c r="AA143" s="51" t="n"/>
-      <c r="AB143" s="51" t="n"/>
-      <c r="AC143" s="51" t="n"/>
-      <c r="AD143" s="51" t="n"/>
-      <c r="AE143" s="51" t="n"/>
-      <c r="AF143" s="51" t="n"/>
-      <c r="AG143" s="51" t="n"/>
-      <c r="AH143" s="51" t="n"/>
-      <c r="AI143" s="51" t="n"/>
-      <c r="AJ143" s="51" t="n"/>
-      <c r="AK143" s="51" t="n"/>
-      <c r="AL143" s="51" t="n"/>
-      <c r="AM143" s="51" t="n"/>
-      <c r="AN143" s="51" t="n"/>
-      <c r="AO143" s="51" t="n"/>
-      <c r="AP143" s="51" t="n"/>
-      <c r="AQ143" s="51" t="n"/>
-      <c r="AR143" s="51" t="n"/>
-      <c r="AS143" s="51" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:AD75"/>

--- a/北京中心顾问薪酬绩效台账_v3.xlsx
+++ b/北京中心顾问薪酬绩效台账_v3.xlsx
@@ -369,7 +369,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="11"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -559,6 +559,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -38688,30 +38691,80 @@
       <c r="AQ5" s="37" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="n"/>
-      <c r="B6" s="38" t="n"/>
-      <c r="C6" s="38" t="n"/>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n"/>
-      <c r="F6" s="44" t="n"/>
-      <c r="G6" s="44" t="n"/>
-      <c r="H6" s="44" t="n"/>
-      <c r="I6" s="44" t="n"/>
-      <c r="J6" s="44" t="n"/>
-      <c r="K6" s="44" t="n"/>
-      <c r="L6" s="44" t="n"/>
-      <c r="M6" s="44" t="n"/>
-      <c r="N6" s="45" t="n"/>
-      <c r="O6" s="45" t="n"/>
-      <c r="P6" s="48" t="n"/>
-      <c r="Q6" s="44" t="n"/>
-      <c r="R6" s="44" t="n"/>
-      <c r="S6" s="48" t="n"/>
-      <c r="T6" s="48" t="n"/>
-      <c r="U6" s="44" t="n"/>
-      <c r="V6" s="44" t="n"/>
-      <c r="W6" s="45" t="n"/>
-      <c r="X6" s="44" t="n"/>
+      <c r="A6" s="52" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B6" s="53" t="inlineStr">
+        <is>
+          <t>赵星火</t>
+        </is>
+      </c>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D6" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E6" s="53" t="inlineStr">
+        <is>
+          <t>A级学习顾问</t>
+        </is>
+      </c>
+      <c r="F6" s="54">
+        <f>G6+H6</f>
+        <v/>
+      </c>
+      <c r="G6" s="54" t="n">
+        <v>800</v>
+      </c>
+      <c r="H6" s="54">
+        <f>P6+T6</f>
+        <v/>
+      </c>
+      <c r="I6" s="54" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="J6" s="54" t="n">
+        <v>756273.4000000001</v>
+      </c>
+      <c r="K6" s="54" t="n"/>
+      <c r="L6" s="54" t="n">
+        <v>58684.89999999999</v>
+      </c>
+      <c r="M6" s="54" t="n">
+        <v>814958.3000000002</v>
+      </c>
+      <c r="N6" s="55" t="n">
+        <v>0.708659391304348</v>
+      </c>
+      <c r="O6" s="55" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="P6" s="75" t="n">
+        <v>6519.666400000002</v>
+      </c>
+      <c r="Q6" s="54" t="n"/>
+      <c r="R6" s="54" t="n"/>
+      <c r="S6" s="55" t="n"/>
+      <c r="T6" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="54" t="n">
+        <v>80</v>
+      </c>
+      <c r="V6" s="54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W6" s="55" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X6" s="54" t="n">
+        <v>800</v>
+      </c>
       <c r="Y6" s="37" t="n"/>
       <c r="Z6" s="37" t="n"/>
       <c r="AA6" s="37" t="n"/>
@@ -38733,30 +38786,80 @@
       <c r="AQ6" s="37" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="n"/>
-      <c r="B7" s="38" t="n"/>
-      <c r="C7" s="38" t="n"/>
-      <c r="D7" s="38" t="n"/>
-      <c r="E7" s="38" t="n"/>
-      <c r="F7" s="44" t="n"/>
-      <c r="G7" s="44" t="n"/>
-      <c r="H7" s="44" t="n"/>
-      <c r="I7" s="44" t="n"/>
-      <c r="J7" s="44" t="n"/>
-      <c r="K7" s="44" t="n"/>
-      <c r="L7" s="44" t="n"/>
-      <c r="M7" s="44" t="n"/>
-      <c r="N7" s="45" t="n"/>
-      <c r="O7" s="45" t="n"/>
-      <c r="P7" s="48" t="n"/>
-      <c r="Q7" s="44" t="n"/>
-      <c r="R7" s="44" t="n"/>
-      <c r="S7" s="48" t="n"/>
-      <c r="T7" s="48" t="n"/>
-      <c r="U7" s="44" t="n"/>
-      <c r="V7" s="44" t="n"/>
-      <c r="W7" s="45" t="n"/>
-      <c r="X7" s="44" t="n"/>
+      <c r="A7" s="52" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>谭悦</t>
+        </is>
+      </c>
+      <c r="C7" s="53" t="inlineStr">
+        <is>
+          <t>个性化</t>
+        </is>
+      </c>
+      <c r="D7" s="53" t="inlineStr">
+        <is>
+          <t>考研个性化</t>
+        </is>
+      </c>
+      <c r="E7" s="53" t="inlineStr">
+        <is>
+          <t>B级学习顾问</t>
+        </is>
+      </c>
+      <c r="F7" s="54">
+        <f>G7+H7</f>
+        <v/>
+      </c>
+      <c r="G7" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H7" s="54">
+        <f>P7+T7</f>
+        <v/>
+      </c>
+      <c r="I7" s="54" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="J7" s="54" t="n">
+        <v>1248267</v>
+      </c>
+      <c r="K7" s="54" t="n"/>
+      <c r="L7" s="54" t="n">
+        <v>41749.7</v>
+      </c>
+      <c r="M7" s="54" t="n">
+        <v>1290016.7</v>
+      </c>
+      <c r="N7" s="55" t="n">
+        <v>1.172742454545455</v>
+      </c>
+      <c r="O7" s="55" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P7" s="75" t="n">
+        <v>38700.501</v>
+      </c>
+      <c r="Q7" s="54" t="n"/>
+      <c r="R7" s="54" t="n"/>
+      <c r="S7" s="55" t="n"/>
+      <c r="T7" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="54" t="n">
+        <v>100</v>
+      </c>
+      <c r="V7" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W7" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="54" t="n">
+        <v>2000</v>
+      </c>
       <c r="Y7" s="37" t="n"/>
       <c r="Z7" s="37" t="n"/>
       <c r="AA7" s="37" t="n"/>
